--- a/output/pdf_financials_xlsx/ATR.P.xlsx
+++ b/output/pdf_financials_xlsx/ATR.P.xlsx
@@ -2523,16 +2523,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.014329</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.014329</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.014329</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.014329</v>
       </c>
     </row>
     <row r="93">
@@ -3805,7 +3805,11 @@
           <t>Reserves (note 4)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4006,7 +4010,11 @@
           <t>Share-based payments reserve (note 4)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4078,7 +4086,11 @@
           <t>Share-based payments reserve (note 4)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4269,7 +4281,11 @@
           <t>Share-based payment reserve (note 4)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATR.P.xlsx
+++ b/output/pdf_financials_xlsx/ATR.P.xlsx
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.154979</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.278923</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.221973</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.169642</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.113387</v>
       </c>
     </row>
     <row r="35">
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.154979</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.278923</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.221973</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.169642</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.113387</v>
       </c>
     </row>
     <row r="37">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ATR.P.xlsx
+++ b/output/pdf_financials_xlsx/ATR.P.xlsx
@@ -2703,19 +2703,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000575</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.000344</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-6.4e-05</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-2.8e-05</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000417</v>
       </c>
     </row>
     <row r="102">
@@ -2813,19 +2813,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.019862</v>
+        <v>0.019287</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.005212</v>
+        <v>0.005556</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.001176</v>
+        <v>0.001112</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.0009700000000000001</v>
+        <v>0.000942</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.003424</v>
+        <v>-0.003841</v>
       </c>
     </row>
     <row r="107">
@@ -4369,7 +4369,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4869,7 +4873,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.000575</v>
       </c>
@@ -5195,7 +5203,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.17</v>
       </c>
